--- a/logs/experiments_not_systematic/one_head_map_search_optimization/one_head_map_search_optimization.xlsx
+++ b/logs/experiments_not_systematic/one_head_map_search_optimization/one_head_map_search_optimization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/experiments_not_systematic/one_head_map_search_optimization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{896B0358-BF3B-4CC6-BC6B-6DBD13BC3CFF}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09C5E7F7-643B-40FC-A7E7-52AA17DCD557}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main results" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="256">
   <si>
     <t>date</t>
   </si>
@@ -854,7 +854,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -865,12 +865,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9524,8 +9518,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37B8E839-F96B-4695-BBD4-28D863AD6E55}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:L55" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37B8E839-F96B-4695-BBD4-28D863AD6E55}" name="TablaDinámica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:L10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="75">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -9579,19 +9573,19 @@
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="3">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
+        <item x="0"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="7">
         <item sd="0" x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -9650,163 +9644,28 @@
   </pivotFields>
   <rowFields count="4">
     <field x="22"/>
+    <field x="21"/>
     <field x="20"/>
-    <field x="21"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="52">
+  <rowItems count="7">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
     </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
     <i>
       <x v="2"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
     </i>
     <i>
       <x v="3"/>
     </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
     <i>
       <x v="4"/>
     </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
     <i>
       <x v="5"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -34722,21 +34581,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2999E7B8-524B-4164-A89A-1339340538A3}">
-  <dimension ref="A3:L55"/>
+  <dimension ref="A3:L10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="38" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -34820,7 +34679,7 @@
         <v>141</v>
       </c>
       <c r="B5" s="5">
-        <v>0.38881280370071181</v>
+        <v>0.38881280370071186</v>
       </c>
       <c r="C5" s="5">
         <v>-0.3449275073885707</v>
@@ -34829,16 +34688,16 @@
         <v>0.74040551381956066</v>
       </c>
       <c r="E5" s="5">
-        <v>0.26584985448631565</v>
+        <v>0.26584985448631571</v>
       </c>
       <c r="F5" s="5">
-        <v>0.27122796028270102</v>
+        <v>0.27122796028270096</v>
       </c>
       <c r="G5" s="5">
         <v>0.13640301594688375</v>
       </c>
       <c r="H5" s="5">
-        <v>-0.71471875679789743</v>
+        <v>-0.71471875679789754</v>
       </c>
       <c r="I5" s="5">
         <v>-3.8540779118419355E-2</v>
@@ -34854,1902 +34713,192 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>98</v>
+      <c r="A6" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="B6" s="5">
-        <v>0.45057033576190547</v>
+        <v>0.57726562239393553</v>
       </c>
       <c r="C6" s="5">
-        <v>-0.12128517025996415</v>
+        <v>4.9317320570717521E-3</v>
       </c>
       <c r="D6" s="5">
-        <v>0.62138813419833572</v>
+        <v>5.5596361783147689E-2</v>
       </c>
       <c r="E6" s="5">
-        <v>0.29947778206968312</v>
+        <v>0.86584060126161033</v>
       </c>
       <c r="F6" s="5">
-        <v>0.3594629077139137</v>
+        <v>0.80301912935814268</v>
       </c>
       <c r="G6" s="5">
-        <v>0.26539025849349274</v>
+        <v>0.55041440058185487</v>
       </c>
       <c r="H6" s="5">
-        <v>-0.1520312446618681</v>
+        <v>-7.0480482010203066E-3</v>
       </c>
       <c r="I6" s="5">
-        <v>-4.4681454477457028E-2</v>
+        <v>9.2256824250051592E-2</v>
       </c>
       <c r="J6" s="5">
-        <v>1.6371245124973035E-2</v>
+        <v>0.11354400631668028</v>
       </c>
       <c r="K6" s="5">
-        <v>-6.3330335111041761E-2</v>
+        <v>-0.15217485555876853</v>
       </c>
       <c r="L6" s="5">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>1</v>
+      <c r="A7" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="B7" s="5">
-        <v>0.4512388495357666</v>
+        <v>0.49874859397857296</v>
       </c>
       <c r="C7" s="5">
-        <v>-0.20266186830233138</v>
+        <v>-0.42571389458398523</v>
       </c>
       <c r="D7" s="5">
-        <v>0.71863391825093703</v>
+        <v>0.28580144225817122</v>
       </c>
       <c r="E7" s="5">
-        <v>0.20159886267361371</v>
+        <v>0.54088912989218363</v>
       </c>
       <c r="F7" s="5">
-        <v>0.39149405268912085</v>
+        <v>0.5123178553408041</v>
       </c>
       <c r="G7" s="5">
-        <v>0.29642664155419723</v>
+        <v>0.30222444766807355</v>
       </c>
       <c r="H7" s="5">
-        <v>-0.35260695488708094</v>
+        <v>-0.25018601112328898</v>
       </c>
       <c r="I7" s="5">
-        <v>-0.14011598334413874</v>
+        <v>-0.43165619876003186</v>
       </c>
       <c r="J7" s="5">
-        <v>-0.10482193106263639</v>
+        <v>-0.29374457558387823</v>
       </c>
       <c r="K7" s="5">
-        <v>-9.2506504015408428E-2</v>
+        <v>-0.34258676295032586</v>
       </c>
       <c r="L7" s="5">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
-        <v>2</v>
+      <c r="A8" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="B8" s="5">
-        <v>0.44990182198804424</v>
+        <v>0.5183127432767185</v>
       </c>
       <c r="C8" s="5">
-        <v>-3.9908472217596892E-2</v>
+        <v>-1.4714459639019677E-2</v>
       </c>
       <c r="D8" s="5">
-        <v>0.5241423501457344</v>
+        <v>0.17549519950618425</v>
       </c>
       <c r="E8" s="5">
-        <v>0.39735670146575258</v>
+        <v>0.76432342191514813</v>
       </c>
       <c r="F8" s="5">
-        <v>0.3274317627387065</v>
+        <v>0.7038557360983464</v>
       </c>
       <c r="G8" s="5">
-        <v>0.23435387543278829</v>
+        <v>0.38670415294970151</v>
       </c>
       <c r="H8" s="5">
-        <v>4.854446556334472E-2</v>
+        <v>7.8718019639362383E-2</v>
       </c>
       <c r="I8" s="5">
-        <v>5.0753074389224696E-2</v>
+        <v>-8.2295858147006379E-2</v>
       </c>
       <c r="J8" s="5">
-        <v>0.13756442131258245</v>
+        <v>-2.7148222120558802E-3</v>
       </c>
       <c r="K8" s="5">
-        <v>-3.4154166206675093E-2</v>
+        <v>-0.11113866381187298</v>
       </c>
       <c r="L8" s="5">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>87</v>
+      <c r="A9" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="B9" s="5">
-        <v>0.34907312398530305</v>
+        <v>0.43740971611575152</v>
       </c>
       <c r="C9" s="5">
-        <v>-0.40837683694314686</v>
+        <v>0.14132109084805189</v>
       </c>
       <c r="D9" s="5">
-        <v>0.79363465459184379</v>
+        <v>0.35404140292494773</v>
       </c>
       <c r="E9" s="5">
-        <v>0.22711897393053135</v>
+        <v>0.57600547372663369</v>
       </c>
       <c r="F9" s="5">
-        <v>0.21688852191671937</v>
+        <v>0.66510574467229067</v>
       </c>
       <c r="G9" s="5">
-        <v>8.3745008193117809E-2</v>
+        <v>0.13065370834142198</v>
       </c>
       <c r="H9" s="5">
-        <v>-0.7605302378279224</v>
+        <v>-0.11906420689696035</v>
       </c>
       <c r="I9" s="5">
-        <v>-4.2253288521562925E-2</v>
+        <v>0.28151544116557842</v>
       </c>
       <c r="J9" s="5">
-        <v>-1.5078302276993935E-2</v>
+        <v>0.39233368945831226</v>
       </c>
       <c r="K9" s="5">
-        <v>-5.0634569573691328E-2</v>
+        <v>3.3216971587337082E-3</v>
       </c>
       <c r="L9" s="5">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
-        <v>1</v>
+      <c r="A10" s="4" t="s">
+        <v>162</v>
       </c>
       <c r="B10" s="5">
-        <v>0.23945204122230654</v>
+        <v>0.48038761352538978</v>
       </c>
       <c r="C10" s="5">
-        <v>-0.52282563620483136</v>
+        <v>-9.2899865713453142E-2</v>
       </c>
       <c r="D10" s="5">
-        <v>0.89527034779397141</v>
+        <v>0.32353551655531942</v>
       </c>
       <c r="E10" s="5">
-        <v>1.0978003348556734E-2</v>
+        <v>0.59935127926592469</v>
       </c>
       <c r="F10" s="5">
-        <v>8.6394773544027723E-3</v>
+        <v>0.58270419240173077</v>
       </c>
       <c r="G10" s="5">
-        <v>1.7659162541958501E-2</v>
+        <v>0.29683109460903601</v>
       </c>
       <c r="H10" s="5">
-        <v>-1.1238611336052751</v>
+        <v>-0.17915624404180225</v>
       </c>
       <c r="I10" s="5">
-        <v>-3.7063404660596287E-2</v>
+        <v>2.2404894928492953E-3</v>
       </c>
       <c r="J10" s="5">
-        <v>-2.7233731846902993E-2</v>
+        <v>7.9613468041370233E-2</v>
       </c>
       <c r="K10" s="5">
-        <v>-2.8323988096141745E-2</v>
+        <v>-0.1122176265297809</v>
       </c>
       <c r="L10" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
-        <v>2</v>
-      </c>
-      <c r="B11" s="5">
-        <v>0.45869420674829953</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-0.29392803768146242</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0.69199896138971606</v>
-      </c>
-      <c r="E11" s="5">
-        <v>0.44325994451250589</v>
-      </c>
-      <c r="F11" s="5">
-        <v>0.425137566479036</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.14983085384427711</v>
-      </c>
-      <c r="H11" s="5">
-        <v>-0.39719934205056995</v>
-      </c>
-      <c r="I11" s="5">
-        <v>-4.7443172382529548E-2</v>
-      </c>
-      <c r="J11" s="5">
-        <v>-2.922872707084872E-3</v>
-      </c>
-      <c r="K11" s="5">
-        <v>-7.29451510512409E-2</v>
-      </c>
-      <c r="L11" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="5">
-        <v>0.36679495135492696</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-0.50512051496260102</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0.80619375266850302</v>
-      </c>
-      <c r="E12" s="5">
-        <v>0.27095280745873268</v>
-      </c>
-      <c r="F12" s="5">
-        <v>0.23733245121746985</v>
-      </c>
-      <c r="G12" s="5">
-        <v>6.0073781154040662E-2</v>
-      </c>
-      <c r="H12" s="5">
-        <v>-1.2315947879039022</v>
-      </c>
-      <c r="I12" s="5">
-        <v>-2.8687594356238102E-2</v>
-      </c>
-      <c r="J12" s="5">
-        <v>1.5343734521459558E-3</v>
-      </c>
-      <c r="K12" s="5">
-        <v>2.8504268026866945E-3</v>
-      </c>
-      <c r="L12" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
-        <v>1</v>
-      </c>
-      <c r="B13" s="5">
-        <v>0.22533733461207861</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-0.48731451134657489</v>
-      </c>
-      <c r="D13" s="5">
-        <v>0.8894645808774998</v>
-      </c>
-      <c r="E13" s="5">
-        <v>2.0900651997009193E-2</v>
-      </c>
-      <c r="F13" s="5">
-        <v>1.1338287286547141E-2</v>
-      </c>
-      <c r="G13" s="5">
-        <v>-1.734343660586557E-4</v>
-      </c>
-      <c r="H13" s="5">
-        <v>-1.0664658686725679</v>
-      </c>
-      <c r="I13" s="5">
-        <v>6.2792827270556168E-3</v>
-      </c>
-      <c r="J13" s="5">
-        <v>1.0143400614503991E-2</v>
-      </c>
-      <c r="K13" s="5">
-        <v>-4.8260770089125033E-3</v>
-      </c>
-      <c r="L13" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="7">
-        <v>2</v>
-      </c>
-      <c r="B14" s="5">
-        <v>0.5082525680977753</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-0.52292651857862715</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0.72292292445950623</v>
-      </c>
-      <c r="E14" s="5">
-        <v>0.52100496292045617</v>
-      </c>
-      <c r="F14" s="5">
-        <v>0.46332661514839257</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0.12032099667413998</v>
-      </c>
-      <c r="H14" s="5">
-        <v>-1.3967237071352363</v>
-      </c>
-      <c r="I14" s="5">
-        <v>-6.3654471439531818E-2</v>
-      </c>
-      <c r="J14" s="5">
-        <v>-7.0746537102120794E-3</v>
-      </c>
-      <c r="K14" s="5">
-        <v>1.0526930614285892E-2</v>
-      </c>
-      <c r="L14" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="5">
-        <v>0.57726562239393553</v>
-      </c>
-      <c r="C15" s="5">
-        <v>4.9317320570717998E-3</v>
-      </c>
-      <c r="D15" s="5">
-        <v>5.5596361783147703E-2</v>
-      </c>
-      <c r="E15" s="5">
-        <v>0.86584060126161033</v>
-      </c>
-      <c r="F15" s="5">
-        <v>0.80301912935814257</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0.5504144005818552</v>
-      </c>
-      <c r="H15" s="5">
-        <v>-7.0480482010203066E-3</v>
-      </c>
-      <c r="I15" s="5">
-        <v>9.2256824250051592E-2</v>
-      </c>
-      <c r="J15" s="5">
-        <v>0.11354400631668025</v>
-      </c>
-      <c r="K15" s="5">
-        <v>-0.15217485555876856</v>
-      </c>
-      <c r="L15" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" s="5">
-        <v>0.57289566398559288</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0.24498100126893177</v>
-      </c>
-      <c r="D16" s="5">
-        <v>2.1464379226993045E-2</v>
-      </c>
-      <c r="E16" s="5">
-        <v>0.88148639171521248</v>
-      </c>
-      <c r="F16" s="5">
-        <v>0.79326574533754435</v>
-      </c>
-      <c r="G16" s="5">
-        <v>0.5606376690495779</v>
-      </c>
-      <c r="H16" s="5">
-        <v>-3.1824165996228226E-2</v>
-      </c>
-      <c r="I16" s="5">
-        <v>0.4447628731768572</v>
-      </c>
-      <c r="J16" s="5">
-        <v>0.34347618314686074</v>
-      </c>
-      <c r="K16" s="5">
-        <v>0.18120787767419835</v>
-      </c>
-      <c r="L16" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="7">
-        <v>1</v>
-      </c>
-      <c r="B17" s="5">
-        <v>0.66383684707962776</v>
-      </c>
-      <c r="C17" s="5">
-        <v>0.37834114749734399</v>
-      </c>
-      <c r="D17" s="5">
-        <v>2.2601947846949532E-2</v>
-      </c>
-      <c r="E17" s="5">
-        <v>0.94504021713807151</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0.87720825907510669</v>
-      </c>
-      <c r="G17" s="5">
-        <v>0.82403046446928219</v>
-      </c>
-      <c r="H17" s="5">
-        <v>-1.1405430870144969E-2</v>
-      </c>
-      <c r="I17" s="5">
-        <v>0.70374208051345255</v>
-      </c>
-      <c r="J17" s="5">
-        <v>0.43096841154740506</v>
-      </c>
-      <c r="K17" s="5">
-        <v>0.354794640388639</v>
-      </c>
-      <c r="L17" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="7">
-        <v>2</v>
-      </c>
-      <c r="B18" s="5">
-        <v>0.48195448089155796</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0.11162085504051951</v>
-      </c>
-      <c r="D18" s="5">
-        <v>2.0326810607036561E-2</v>
-      </c>
-      <c r="E18" s="5">
-        <v>0.81793256629235334</v>
-      </c>
-      <c r="F18" s="5">
-        <v>0.70932323159998212</v>
-      </c>
-      <c r="G18" s="5">
-        <v>0.29724487362987351</v>
-      </c>
-      <c r="H18" s="5">
-        <v>-5.2242901122311482E-2</v>
-      </c>
-      <c r="I18" s="5">
-        <v>0.18578366584026185</v>
-      </c>
-      <c r="J18" s="5">
-        <v>0.25598395474631641</v>
-      </c>
-      <c r="K18" s="5">
-        <v>7.6211149597577481E-3</v>
-      </c>
-      <c r="L18" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="5">
-        <v>0.5916742438503807</v>
-      </c>
-      <c r="C19" s="5">
-        <v>2.1618186547838526E-2</v>
-      </c>
-      <c r="D19" s="5">
-        <v>7.4316101542125798E-2</v>
-      </c>
-      <c r="E19" s="5">
-        <v>0.84145461438764968</v>
-      </c>
-      <c r="F19" s="5">
-        <v>0.79243311780605863</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0.64234773385073574</v>
-      </c>
-      <c r="H19" s="5">
-        <v>2.0123596619915588E-3</v>
-      </c>
-      <c r="I19" s="5">
-        <v>0.21007019900077537</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0.27020125508512705</v>
-      </c>
-      <c r="K19" s="5">
-        <v>-0.28717971059493147</v>
-      </c>
-      <c r="L19" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="7">
-        <v>1</v>
-      </c>
-      <c r="B20" s="5">
-        <v>0.67460144977308334</v>
-      </c>
-      <c r="C20" s="5">
-        <v>0.38534329454496929</v>
-      </c>
-      <c r="D20" s="5">
-        <v>4.2739871423871624E-2</v>
-      </c>
-      <c r="E20" s="5">
-        <v>0.95125742303489014</v>
-      </c>
-      <c r="F20" s="5">
-        <v>0.88858528057444663</v>
-      </c>
-      <c r="G20" s="5">
-        <v>0.81635008842753065</v>
-      </c>
-      <c r="H20" s="5">
-        <v>4.7462966188487277E-2</v>
-      </c>
-      <c r="I20" s="5">
-        <v>0.72191412645764663</v>
-      </c>
-      <c r="J20" s="5">
-        <v>0.56718001929156558</v>
-      </c>
-      <c r="K20" s="5">
-        <v>0.18383805512103699</v>
-      </c>
-      <c r="L20" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="7">
-        <v>2</v>
-      </c>
-      <c r="B21" s="5">
-        <v>0.50874703792767817</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-0.34210692144929222</v>
-      </c>
-      <c r="D21" s="5">
-        <v>0.10589233166037998</v>
-      </c>
-      <c r="E21" s="5">
-        <v>0.73165180574040922</v>
-      </c>
-      <c r="F21" s="5">
-        <v>0.69628095503767062</v>
-      </c>
-      <c r="G21" s="5">
-        <v>0.46834537927394077</v>
-      </c>
-      <c r="H21" s="5">
-        <v>-4.3438246864504156E-2</v>
-      </c>
-      <c r="I21" s="5">
-        <v>-0.30177372845609596</v>
-      </c>
-      <c r="J21" s="5">
-        <v>-2.6777509121311483E-2</v>
-      </c>
-      <c r="K21" s="5">
-        <v>-0.75819747631089973</v>
-      </c>
-      <c r="L21" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B22" s="5">
-        <v>0.56722695934583278</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-0.251803991645555</v>
-      </c>
-      <c r="D22" s="5">
-        <v>7.1008604580324222E-2</v>
-      </c>
-      <c r="E22" s="5">
-        <v>0.87458079768196939</v>
-      </c>
-      <c r="F22" s="5">
-        <v>0.82335852493082451</v>
-      </c>
-      <c r="G22" s="5">
-        <v>0.4482577988452518</v>
-      </c>
-      <c r="H22" s="5">
-        <v>8.6676617311757433E-3</v>
-      </c>
-      <c r="I22" s="5">
-        <v>-0.37806259942747783</v>
-      </c>
-      <c r="J22" s="5">
-        <v>-0.27304541928194698</v>
-      </c>
-      <c r="K22" s="5">
-        <v>-0.35055273375557272</v>
-      </c>
-      <c r="L22" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="7">
-        <v>1</v>
-      </c>
-      <c r="B23" s="5">
-        <v>0.60229065167004137</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-0.33600027190517251</v>
-      </c>
-      <c r="D23" s="5">
-        <v>5.3776672514237039E-2</v>
-      </c>
-      <c r="E23" s="5">
-        <v>0.93813990009815795</v>
-      </c>
-      <c r="F23" s="5">
-        <v>0.88463092703335322</v>
-      </c>
-      <c r="G23" s="5">
-        <v>0.53892571752715956</v>
-      </c>
-      <c r="H23" s="5">
-        <v>-8.3634740883355332E-2</v>
-      </c>
-      <c r="I23" s="5">
-        <v>-0.55814243588267753</v>
-      </c>
-      <c r="J23" s="5">
-        <v>-0.33188723970526923</v>
-      </c>
-      <c r="K23" s="5">
-        <v>-0.34567011051925561</v>
-      </c>
-      <c r="L23" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="7">
-        <v>2</v>
-      </c>
-      <c r="B24" s="5">
-        <v>0.53216326702162431</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-0.16760771138593752</v>
-      </c>
-      <c r="D24" s="5">
-        <v>8.8240536646411405E-2</v>
-      </c>
-      <c r="E24" s="5">
-        <v>0.81102169526578083</v>
-      </c>
-      <c r="F24" s="5">
-        <v>0.76208612282829591</v>
-      </c>
-      <c r="G24" s="5">
-        <v>0.35758988016334398</v>
-      </c>
-      <c r="H24" s="5">
-        <v>0.10097006434570682</v>
-      </c>
-      <c r="I24" s="5">
-        <v>-0.19798276297227824</v>
-      </c>
-      <c r="J24" s="5">
-        <v>-0.21420359885862469</v>
-      </c>
-      <c r="K24" s="5">
-        <v>-0.35543535699188977</v>
-      </c>
-      <c r="L24" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B25" s="5">
-        <v>0.49874859397857285</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-0.42571389458398518</v>
-      </c>
-      <c r="D25" s="5">
-        <v>0.28580144225817133</v>
-      </c>
-      <c r="E25" s="5">
-        <v>0.54088912989218363</v>
-      </c>
-      <c r="F25" s="5">
-        <v>0.5123178553408041</v>
-      </c>
-      <c r="G25" s="5">
-        <v>0.30222444766807366</v>
-      </c>
-      <c r="H25" s="5">
-        <v>-0.25018601112328909</v>
-      </c>
-      <c r="I25" s="5">
-        <v>-0.43165619876003192</v>
-      </c>
-      <c r="J25" s="5">
-        <v>-0.29374457558387823</v>
-      </c>
-      <c r="K25" s="5">
-        <v>-0.34258676295032586</v>
-      </c>
-      <c r="L25" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="5">
-        <v>0.5131596583517356</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-0.36946013894520019</v>
-      </c>
-      <c r="D26" s="5">
-        <v>0.34637970109837179</v>
-      </c>
-      <c r="E26" s="5">
-        <v>0.49697569679813536</v>
-      </c>
-      <c r="F26" s="5">
-        <v>0.48004011106349626</v>
-      </c>
-      <c r="G26" s="5">
-        <v>0.33983127547673725</v>
-      </c>
-      <c r="H26" s="5">
-        <v>-0.31417620901802262</v>
-      </c>
-      <c r="I26" s="5">
-        <v>-0.34381348123282174</v>
-      </c>
-      <c r="J26" s="5">
-        <v>-0.17595232457623319</v>
-      </c>
-      <c r="K26" s="5">
-        <v>-0.39831534749058012</v>
-      </c>
-      <c r="L26" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="7">
-        <v>1</v>
-      </c>
-      <c r="B27" s="5">
-        <v>0.62554062294746215</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-0.79447121757044137</v>
-      </c>
-      <c r="D27" s="5">
-        <v>0.32166504623880082</v>
-      </c>
-      <c r="E27" s="5">
-        <v>0.56754186514173732</v>
-      </c>
-      <c r="F27" s="5">
-        <v>0.56018437165061152</v>
-      </c>
-      <c r="G27" s="5">
-        <v>0.54269609656372542</v>
-      </c>
-      <c r="H27" s="5">
-        <v>-0.4372745883965094</v>
-      </c>
-      <c r="I27" s="5">
-        <v>-0.93883827720979485</v>
-      </c>
-      <c r="J27" s="5">
-        <v>-0.64907580322306002</v>
-      </c>
-      <c r="K27" s="5">
-        <v>-0.76005381893694857</v>
-      </c>
-      <c r="L27" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="7">
-        <v>2</v>
-      </c>
-      <c r="B28" s="5">
-        <v>0.40077869375600911</v>
-      </c>
-      <c r="C28" s="5">
-        <v>5.5550939680041093E-2</v>
-      </c>
-      <c r="D28" s="5">
-        <v>0.37109435595794277</v>
-      </c>
-      <c r="E28" s="5">
-        <v>0.42640952845453334</v>
-      </c>
-      <c r="F28" s="5">
-        <v>0.39989585047638104</v>
-      </c>
-      <c r="G28" s="5">
-        <v>0.13696645438974911</v>
-      </c>
-      <c r="H28" s="5">
-        <v>-0.19107782963953579</v>
-      </c>
-      <c r="I28" s="5">
-        <v>0.25121131474415143</v>
-      </c>
-      <c r="J28" s="5">
-        <v>0.29717115407059369</v>
-      </c>
-      <c r="K28" s="5">
-        <v>-3.6576876044211705E-2</v>
-      </c>
-      <c r="L28" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29" s="5">
-        <v>0.46189953914073795</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-0.47220866294179159</v>
-      </c>
-      <c r="D29" s="5">
-        <v>0.192520593150136</v>
-      </c>
-      <c r="E29" s="5">
-        <v>0.51668637613077806</v>
-      </c>
-      <c r="F29" s="5">
-        <v>0.50070938500950735</v>
-      </c>
-      <c r="G29" s="5">
-        <v>0.33838580677437435</v>
-      </c>
-      <c r="H29" s="5">
-        <v>-0.22088947606067874</v>
-      </c>
-      <c r="I29" s="5">
-        <v>-0.64440233558914084</v>
-      </c>
-      <c r="J29" s="5">
-        <v>-0.48651136630478242</v>
-      </c>
-      <c r="K29" s="5">
-        <v>-0.38121444280132161</v>
-      </c>
-      <c r="L29" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="7">
-        <v>1</v>
-      </c>
-      <c r="B30" s="5">
-        <v>0.52677606280705358</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-0.95031401655384207</v>
-      </c>
-      <c r="D30" s="5">
-        <v>3.847145434940747E-2</v>
-      </c>
-      <c r="E30" s="5">
-        <v>0.63550605981186614</v>
-      </c>
-      <c r="F30" s="5">
-        <v>0.59431064495391916</v>
-      </c>
-      <c r="G30" s="5">
-        <v>0.54448367983785184</v>
-      </c>
-      <c r="H30" s="5">
-        <v>-0.33329861152193624</v>
-      </c>
-      <c r="I30" s="5">
-        <v>-1.3344651140404948</v>
-      </c>
-      <c r="J30" s="5">
-        <v>-1.0647241388582036</v>
-      </c>
-      <c r="K30" s="5">
-        <v>-0.74479003717412351</v>
-      </c>
-      <c r="L30" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="7">
-        <v>2</v>
-      </c>
-      <c r="B31" s="5">
-        <v>0.39702301547442248</v>
-      </c>
-      <c r="C31" s="5">
-        <v>5.8966906702589599E-3</v>
-      </c>
-      <c r="D31" s="5">
-        <v>0.34656973195086449</v>
-      </c>
-      <c r="E31" s="5">
-        <v>0.39786669244968992</v>
-      </c>
-      <c r="F31" s="5">
-        <v>0.40710812506509558</v>
-      </c>
-      <c r="G31" s="5">
-        <v>0.13228793371089684</v>
-      </c>
-      <c r="H31" s="5">
-        <v>-0.10848034059942126</v>
-      </c>
-      <c r="I31" s="5">
-        <v>4.566044286221304E-2</v>
-      </c>
-      <c r="J31" s="5">
-        <v>9.1701406248638803E-2</v>
-      </c>
-      <c r="K31" s="5">
-        <v>-1.7638848428519632E-2</v>
-      </c>
-      <c r="L31" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B32" s="5">
-        <v>0.52118658444324506</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-0.43547288186496397</v>
-      </c>
-      <c r="D32" s="5">
-        <v>0.31850403252600601</v>
-      </c>
-      <c r="E32" s="5">
-        <v>0.60900531674763736</v>
-      </c>
-      <c r="F32" s="5">
-        <v>0.55620406994940852</v>
-      </c>
-      <c r="G32" s="5">
-        <v>0.22845626075310924</v>
-      </c>
-      <c r="H32" s="5">
-        <v>-0.21549234829116568</v>
-      </c>
-      <c r="I32" s="5">
-        <v>-0.30675277945813312</v>
-      </c>
-      <c r="J32" s="5">
-        <v>-0.21877003587061913</v>
-      </c>
-      <c r="K32" s="5">
-        <v>-0.24823049855907595</v>
-      </c>
-      <c r="L32" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="7">
-        <v>1</v>
-      </c>
-      <c r="B33" s="5">
-        <v>0.61728376671648244</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-0.76902066788280932</v>
-      </c>
-      <c r="D33" s="5">
-        <v>0.30629533473189952</v>
-      </c>
-      <c r="E33" s="5">
-        <v>0.75938344980842765</v>
-      </c>
-      <c r="F33" s="5">
-        <v>0.71391276211547494</v>
-      </c>
-      <c r="G33" s="5">
-        <v>0.33577463172092098</v>
-      </c>
-      <c r="H33" s="5">
-        <v>-0.22817724450063639</v>
-      </c>
-      <c r="I33" s="5">
-        <v>-0.62892559498955347</v>
-      </c>
-      <c r="J33" s="5">
-        <v>-0.45477578344153907</v>
-      </c>
-      <c r="K33" s="5">
-        <v>-0.52412395088768349</v>
-      </c>
-      <c r="L33" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="7">
-        <v>2</v>
-      </c>
-      <c r="B34" s="5">
-        <v>0.42508940217000785</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-0.10192509584711851</v>
-      </c>
-      <c r="D34" s="5">
-        <v>0.33071273032011239</v>
-      </c>
-      <c r="E34" s="5">
-        <v>0.45862718368684702</v>
-      </c>
-      <c r="F34" s="5">
-        <v>0.39849537778334221</v>
-      </c>
-      <c r="G34" s="5">
-        <v>0.12113788978529753</v>
-      </c>
-      <c r="H34" s="5">
-        <v>-0.20280745208169496</v>
-      </c>
-      <c r="I34" s="5">
-        <v>1.5420036073287227E-2</v>
-      </c>
-      <c r="J34" s="5">
-        <v>1.7235711700300842E-2</v>
-      </c>
-      <c r="K34" s="5">
-        <v>2.7662953769531651E-2</v>
-      </c>
-      <c r="L34" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B35" s="5">
-        <v>0.51831274327671839</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-1.4714459639019677E-2</v>
-      </c>
-      <c r="D35" s="5">
-        <v>0.1754951995061842</v>
-      </c>
-      <c r="E35" s="5">
-        <v>0.76432342191514846</v>
-      </c>
-      <c r="F35" s="5">
-        <v>0.70385573609834662</v>
-      </c>
-      <c r="G35" s="5">
-        <v>0.38670415294970145</v>
-      </c>
-      <c r="H35" s="5">
-        <v>7.8718019639362369E-2</v>
-      </c>
-      <c r="I35" s="5">
-        <v>-8.2295858147006379E-2</v>
-      </c>
-      <c r="J35" s="5">
-        <v>-2.7148222120558846E-3</v>
-      </c>
-      <c r="K35" s="5">
-        <v>-0.11113866381187298</v>
-      </c>
-      <c r="L35" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B36" s="5">
-        <v>0.5601308434124237</v>
-      </c>
-      <c r="C36" s="5">
-        <v>7.5447093290681458E-2</v>
-      </c>
-      <c r="D36" s="5">
-        <v>0.25000153870036373</v>
-      </c>
-      <c r="E36" s="5">
-        <v>0.77496668540107805</v>
-      </c>
-      <c r="F36" s="5">
-        <v>0.75339251864007373</v>
-      </c>
-      <c r="G36" s="5">
-        <v>0.42159475431731658</v>
-      </c>
-      <c r="H36" s="5">
-        <v>6.7610520723654463E-2</v>
-      </c>
-      <c r="I36" s="5">
-        <v>7.2570994868530053E-2</v>
-      </c>
-      <c r="J36" s="5">
-        <v>7.7880977995827147E-2</v>
-      </c>
-      <c r="K36" s="5">
-        <v>-9.3969243136080058E-2</v>
-      </c>
-      <c r="L36" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="7">
-        <v>1</v>
-      </c>
-      <c r="B37" s="5">
-        <v>0.6138157437778643</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-3.4862205004359361E-3</v>
-      </c>
-      <c r="D37" s="5">
-        <v>0.16922130705442448</v>
-      </c>
-      <c r="E37" s="5">
-        <v>0.81835098263436146</v>
-      </c>
-      <c r="F37" s="5">
-        <v>0.78534528081842669</v>
-      </c>
-      <c r="G37" s="5">
-        <v>0.63761387382735257</v>
-      </c>
-      <c r="H37" s="5">
-        <v>-2.3778768328583045E-2</v>
-      </c>
-      <c r="I37" s="5">
-        <v>-3.2207113447426022E-2</v>
-      </c>
-      <c r="J37" s="5">
-        <v>1.1624500593604351E-2</v>
-      </c>
-      <c r="K37" s="5">
-        <v>-0.21691001356242637</v>
-      </c>
-      <c r="L37" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="7">
-        <v>2</v>
-      </c>
-      <c r="B38" s="5">
-        <v>0.5064459430469832</v>
-      </c>
-      <c r="C38" s="5">
-        <v>0.15438040708179887</v>
-      </c>
-      <c r="D38" s="5">
-        <v>0.33078177034630302</v>
-      </c>
-      <c r="E38" s="5">
-        <v>0.73158238816779464</v>
-      </c>
-      <c r="F38" s="5">
-        <v>0.72143975646172065</v>
-      </c>
-      <c r="G38" s="5">
-        <v>0.2055756348072805</v>
-      </c>
-      <c r="H38" s="5">
-        <v>0.15899980977589198</v>
-      </c>
-      <c r="I38" s="5">
-        <v>0.17734910318448613</v>
-      </c>
-      <c r="J38" s="5">
-        <v>0.14413745539804992</v>
-      </c>
-      <c r="K38" s="5">
-        <v>2.897152729026627E-2</v>
-      </c>
-      <c r="L38" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" s="5">
-        <v>0.51560716945070195</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-1.8943057246910543E-2</v>
-      </c>
-      <c r="D39" s="5">
-        <v>0.13005486076672015</v>
-      </c>
-      <c r="E39" s="5">
-        <v>0.80693315314510672</v>
-      </c>
-      <c r="F39" s="5">
-        <v>0.70838710624479229</v>
-      </c>
-      <c r="G39" s="5">
-        <v>0.36247944190169884</v>
-      </c>
-      <c r="H39" s="5">
-        <v>9.5116178249819106E-2</v>
-      </c>
-      <c r="I39" s="5">
-        <v>-0.10841000750147917</v>
-      </c>
-      <c r="J39" s="5">
-        <v>-9.1261657539539756E-2</v>
-      </c>
-      <c r="K39" s="5">
-        <v>-3.9917016526826311E-2</v>
-      </c>
-      <c r="L39" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="7">
-        <v>1</v>
-      </c>
-      <c r="B40" s="5">
-        <v>0.55260196350000446</v>
-      </c>
-      <c r="C40" s="5">
-        <v>8.6096849761306923E-2</v>
-      </c>
-      <c r="D40" s="5">
-        <v>9.2256390976537261E-2</v>
-      </c>
-      <c r="E40" s="5">
-        <v>0.81968169121487156</v>
-      </c>
-      <c r="F40" s="5">
-        <v>0.74776498923801249</v>
-      </c>
-      <c r="G40" s="5">
-        <v>0.47306152227834614</v>
-      </c>
-      <c r="H40" s="5">
-        <v>4.1738881638607672E-2</v>
-      </c>
-      <c r="I40" s="5">
-        <v>1.4359642655774635E-2</v>
-      </c>
-      <c r="J40" s="5">
-        <v>0.12750077329609397</v>
-      </c>
-      <c r="K40" s="5">
-        <v>-3.3430254747818938E-2</v>
-      </c>
-      <c r="L40" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="7">
-        <v>2</v>
-      </c>
-      <c r="B41" s="5">
-        <v>0.4786123754013995</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-0.123982964255128</v>
-      </c>
-      <c r="D41" s="5">
-        <v>0.16785333055690307</v>
-      </c>
-      <c r="E41" s="5">
-        <v>0.79418461507534188</v>
-      </c>
-      <c r="F41" s="5">
-        <v>0.66900922325157242</v>
-      </c>
-      <c r="G41" s="5">
-        <v>0.25189736152505154</v>
-      </c>
-      <c r="H41" s="5">
-        <v>0.14849347486103057</v>
-      </c>
-      <c r="I41" s="5">
-        <v>-0.23117965765873297</v>
-      </c>
-      <c r="J41" s="5">
-        <v>-0.31002408837517348</v>
-      </c>
-      <c r="K41" s="5">
-        <v>-4.6403778305833678E-2</v>
-      </c>
-      <c r="L41" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B42" s="5">
-        <v>0.47920021696702975</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-0.10064741496082996</v>
-      </c>
-      <c r="D42" s="5">
-        <v>0.1464291990514687</v>
-      </c>
-      <c r="E42" s="5">
-        <v>0.71107042719926028</v>
-      </c>
-      <c r="F42" s="5">
-        <v>0.64978758341017306</v>
-      </c>
-      <c r="G42" s="5">
-        <v>0.37603826263008894</v>
-      </c>
-      <c r="H42" s="5">
-        <v>7.3427359944613579E-2</v>
-      </c>
-      <c r="I42" s="5">
-        <v>-0.21104856180807</v>
-      </c>
-      <c r="J42" s="5">
-        <v>5.2362129075449642E-3</v>
-      </c>
-      <c r="K42" s="5">
-        <v>-0.19952973177271258</v>
-      </c>
-      <c r="L42" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="7">
-        <v>1</v>
-      </c>
-      <c r="B43" s="5">
-        <v>0.47495908583426649</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-0.16080439668085547</v>
-      </c>
-      <c r="D43" s="5">
-        <v>1.9852436669001865E-2</v>
-      </c>
-      <c r="E43" s="5">
-        <v>0.7528647174349179</v>
-      </c>
-      <c r="F43" s="5">
-        <v>0.70406124775120971</v>
-      </c>
-      <c r="G43" s="5">
-        <v>0.40073426115798055</v>
-      </c>
-      <c r="H43" s="5">
-        <v>4.2528533301350951E-2</v>
-      </c>
-      <c r="I43" s="5">
-        <v>-0.44158629201752914</v>
-      </c>
-      <c r="J43" s="5">
-        <v>-4.8471008099195689E-3</v>
-      </c>
-      <c r="K43" s="5">
-        <v>-0.22824448664786257</v>
-      </c>
-      <c r="L43" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="7">
-        <v>2</v>
-      </c>
-      <c r="B44" s="5">
-        <v>0.483441348099793</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-4.0490433240804438E-2</v>
-      </c>
-      <c r="D44" s="5">
-        <v>0.27300596143393557</v>
-      </c>
-      <c r="E44" s="5">
-        <v>0.66927613696360255</v>
-      </c>
-      <c r="F44" s="5">
-        <v>0.59551391906913631</v>
-      </c>
-      <c r="G44" s="5">
-        <v>0.35134226410219749</v>
-      </c>
-      <c r="H44" s="5">
-        <v>0.10432618658787619</v>
-      </c>
-      <c r="I44" s="5">
-        <v>1.9489168401389135E-2</v>
-      </c>
-      <c r="J44" s="5">
-        <v>1.5319526625009497E-2</v>
-      </c>
-      <c r="K44" s="5">
-        <v>-0.17081497689756256</v>
-      </c>
-      <c r="L44" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B45" s="5">
-        <v>0.43740971611575158</v>
-      </c>
-      <c r="C45" s="5">
-        <v>0.14132109084805186</v>
-      </c>
-      <c r="D45" s="5">
-        <v>0.35404140292494768</v>
-      </c>
-      <c r="E45" s="5">
-        <v>0.57600547372663358</v>
-      </c>
-      <c r="F45" s="5">
-        <v>0.66510574467229067</v>
-      </c>
-      <c r="G45" s="5">
-        <v>0.13065370834142198</v>
-      </c>
-      <c r="H45" s="5">
-        <v>-0.11906420689696035</v>
-      </c>
-      <c r="I45" s="5">
-        <v>0.28151544116557842</v>
-      </c>
-      <c r="J45" s="5">
-        <v>0.39233368945831237</v>
-      </c>
-      <c r="K45" s="5">
-        <v>3.3216971587337082E-3</v>
-      </c>
-      <c r="L45" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B46" s="5">
-        <v>0.51653299765072724</v>
-      </c>
-      <c r="C46" s="5">
-        <v>0.25452422776537131</v>
-      </c>
-      <c r="D46" s="5">
-        <v>0.38641688657473017</v>
-      </c>
-      <c r="E46" s="5">
-        <v>0.69438217238658384</v>
-      </c>
-      <c r="F46" s="5">
-        <v>0.78766274978572393</v>
-      </c>
-      <c r="G46" s="5">
-        <v>0.14344970039779883</v>
-      </c>
-      <c r="H46" s="5">
-        <v>-0.1287801191866593</v>
-      </c>
-      <c r="I46" s="5">
-        <v>0.51722298549684764</v>
-      </c>
-      <c r="J46" s="5">
-        <v>0.58069840693139196</v>
-      </c>
-      <c r="K46" s="5">
-        <v>2.2986249696157295E-2</v>
-      </c>
-      <c r="L46" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="7">
-        <v>1</v>
-      </c>
-      <c r="B47" s="5">
-        <v>0.51089315786734568</v>
-      </c>
-      <c r="C47" s="5">
-        <v>0.31613870598685806</v>
-      </c>
-      <c r="D47" s="5">
-        <v>0.28381595113495078</v>
-      </c>
-      <c r="E47" s="5">
-        <v>0.69934830734722297</v>
-      </c>
-      <c r="F47" s="5">
-        <v>0.83227867361021912</v>
-      </c>
-      <c r="G47" s="5">
-        <v>0.16816237476339291</v>
-      </c>
-      <c r="H47" s="5">
-        <v>-0.27615557348357217</v>
-      </c>
-      <c r="I47" s="5">
-        <v>0.68962093642462452</v>
-      </c>
-      <c r="J47" s="5">
-        <v>0.8085982772193514</v>
-      </c>
-      <c r="K47" s="5">
-        <v>2.7451850015895157E-2</v>
-      </c>
-      <c r="L47" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="7">
-        <v>2</v>
-      </c>
-      <c r="B48" s="5">
-        <v>0.52217283743410892</v>
-      </c>
-      <c r="C48" s="5">
-        <v>0.1929097495438846</v>
-      </c>
-      <c r="D48" s="5">
-        <v>0.48901782201450961</v>
-      </c>
-      <c r="E48" s="5">
-        <v>0.68941603742594493</v>
-      </c>
-      <c r="F48" s="5">
-        <v>0.74304682596122873</v>
-      </c>
-      <c r="G48" s="5">
-        <v>0.11873702603220478</v>
-      </c>
-      <c r="H48" s="5">
-        <v>1.8595335110253564E-2</v>
-      </c>
-      <c r="I48" s="5">
-        <v>0.34482503456907088</v>
-      </c>
-      <c r="J48" s="5">
-        <v>0.35279853664343247</v>
-      </c>
-      <c r="K48" s="5">
-        <v>1.8520649376419434E-2</v>
-      </c>
-      <c r="L48" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B49" s="5">
-        <v>0.4107712263729606</v>
-      </c>
-      <c r="C49" s="5">
-        <v>0.1025180715015888</v>
-      </c>
-      <c r="D49" s="5">
-        <v>0.33772107419067016</v>
-      </c>
-      <c r="E49" s="5">
-        <v>0.57069592110497291</v>
-      </c>
-      <c r="F49" s="5">
-        <v>0.64812887859284618</v>
-      </c>
-      <c r="G49" s="5">
-        <v>0.1055553089493142</v>
-      </c>
-      <c r="H49" s="5">
-        <v>-9.6441530814164414E-2</v>
-      </c>
-      <c r="I49" s="5">
-        <v>0.24968918083729844</v>
-      </c>
-      <c r="J49" s="5">
-        <v>0.34404482638119066</v>
-      </c>
-      <c r="K49" s="5">
-        <v>-4.1257583762440216E-2</v>
-      </c>
-      <c r="L49" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="7">
-        <v>1</v>
-      </c>
-      <c r="B50" s="5">
-        <v>0.44159419412147088</v>
-      </c>
-      <c r="C50" s="5">
-        <v>0.28743008411231286</v>
-      </c>
-      <c r="D50" s="5">
-        <v>0.30466336353257728</v>
-      </c>
-      <c r="E50" s="5">
-        <v>0.62815750637619383</v>
-      </c>
-      <c r="F50" s="5">
-        <v>0.73208768374144262</v>
-      </c>
-      <c r="G50" s="5">
-        <v>0.10764524266119437</v>
-      </c>
-      <c r="H50" s="5">
-        <v>-0.2265754064982485</v>
-      </c>
-      <c r="I50" s="5">
-        <v>0.67226067232492459</v>
-      </c>
-      <c r="J50" s="5">
-        <v>0.77753120562933453</v>
-      </c>
-      <c r="K50" s="5">
-        <v>-1.0945093202310654E-3</v>
-      </c>
-      <c r="L50" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="7">
-        <v>2</v>
-      </c>
-      <c r="B51" s="5">
-        <v>0.37994825862445031</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-8.2393941109135269E-2</v>
-      </c>
-      <c r="D51" s="5">
-        <v>0.37077878484876309</v>
-      </c>
-      <c r="E51" s="5">
-        <v>0.513234335833752</v>
-      </c>
-      <c r="F51" s="5">
-        <v>0.56417007344424963</v>
-      </c>
-      <c r="G51" s="5">
-        <v>0.10346537523743403</v>
-      </c>
-      <c r="H51" s="5">
-        <v>3.3692344869919677E-2</v>
-      </c>
-      <c r="I51" s="5">
-        <v>-0.17288231065032766</v>
-      </c>
-      <c r="J51" s="5">
-        <v>-8.9441552866953211E-2</v>
-      </c>
-      <c r="K51" s="5">
-        <v>-8.1420658204649374E-2</v>
-      </c>
-      <c r="L51" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B52" s="5">
-        <v>0.38492492432356668</v>
-      </c>
-      <c r="C52" s="5">
-        <v>6.6920973277195359E-2</v>
-      </c>
-      <c r="D52" s="5">
-        <v>0.33798624800944294</v>
-      </c>
-      <c r="E52" s="5">
-        <v>0.4629383276883437</v>
-      </c>
-      <c r="F52" s="5">
-        <v>0.55952560563830211</v>
-      </c>
-      <c r="G52" s="5">
-        <v>0.14295611567715291</v>
-      </c>
-      <c r="H52" s="5">
-        <v>-0.13197097069005723</v>
-      </c>
-      <c r="I52" s="5">
-        <v>7.7634157162589215E-2</v>
-      </c>
-      <c r="J52" s="5">
-        <v>0.2522578350623545</v>
-      </c>
-      <c r="K52" s="5">
-        <v>2.823642554248405E-2</v>
-      </c>
-      <c r="L52" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="7">
-        <v>1</v>
-      </c>
-      <c r="B53" s="5">
-        <v>0.36720975801667244</v>
-      </c>
-      <c r="C53" s="5">
-        <v>0.20944589626250218</v>
-      </c>
-      <c r="D53" s="5">
-        <v>0.35779118876907551</v>
-      </c>
-      <c r="E53" s="5">
-        <v>0.42199074244048734</v>
-      </c>
-      <c r="F53" s="5">
-        <v>0.58996741660483298</v>
-      </c>
-      <c r="G53" s="5">
-        <v>0.10861229354251208</v>
-      </c>
-      <c r="H53" s="5">
-        <v>-0.31238157277363476</v>
-      </c>
-      <c r="I53" s="5">
-        <v>0.38005118683035466</v>
-      </c>
-      <c r="J53" s="5">
-        <v>0.63718775538467065</v>
-      </c>
-      <c r="K53" s="5">
-        <v>8.9602771825356434E-2</v>
-      </c>
-      <c r="L53" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="7">
-        <v>2</v>
-      </c>
-      <c r="B54" s="5">
-        <v>0.40264009063046097</v>
-      </c>
-      <c r="C54" s="5">
-        <v>-7.5603949708111434E-2</v>
-      </c>
-      <c r="D54" s="5">
-        <v>0.31818130724981031</v>
-      </c>
-      <c r="E54" s="5">
-        <v>0.50388591293620022</v>
-      </c>
-      <c r="F54" s="5">
-        <v>0.52908379467177125</v>
-      </c>
-      <c r="G54" s="5">
-        <v>0.17729993781179376</v>
-      </c>
-      <c r="H54" s="5">
-        <v>4.843963139352029E-2</v>
-      </c>
-      <c r="I54" s="5">
-        <v>-0.22478287250517623</v>
-      </c>
-      <c r="J54" s="5">
-        <v>-0.13267208525996158</v>
-      </c>
-      <c r="K54" s="5">
-        <v>-3.3129920740388341E-2</v>
-      </c>
-      <c r="L54" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B55" s="5">
-        <v>0.48038761352538972</v>
-      </c>
-      <c r="C55" s="5">
-        <v>-9.2899865713453156E-2</v>
-      </c>
-      <c r="D55" s="5">
-        <v>0.32353551655531959</v>
-      </c>
-      <c r="E55" s="5">
-        <v>0.59935127926592469</v>
-      </c>
-      <c r="F55" s="5">
-        <v>0.58270419240173077</v>
-      </c>
-      <c r="G55" s="5">
-        <v>0.29683109460903601</v>
-      </c>
-      <c r="H55" s="5">
-        <v>-0.17915624404180217</v>
-      </c>
-      <c r="I55" s="5">
-        <v>2.240489492849294E-3</v>
-      </c>
-      <c r="J55" s="5">
-        <v>7.9613468041370206E-2</v>
-      </c>
-      <c r="K55" s="5">
-        <v>-0.1122176265297809</v>
-      </c>
-      <c r="L55" s="5">
         <v>108</v>
       </c>
     </row>
